--- a/stories/arbres/ATOM-FAM.VER.001-08.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Céline est dans le salon. Papa plie le linge. Ça sent le propre. Céline veut aider. Elle prend un panier. Le panier glisse. Les chaussettes tombent. Le sol est couvert. Céline a le ventre serré. Elle va vers papa. Céline dit : papa, le panier est tombé. Papa s'approche. Papa dit : merci de raconter. On ramasse ensemble. Céline prend une chaussette. Papa tient le panier. Maman entre. Céline dit : maman, j'ai raconté. Le panier est tombé. Maman écoute. Maman dit : merci Céline. On raconte à papa ou maman. C'est comme ça.</t>
+          <t>Céline est dans le salon. Papa plie le linge. Ça sent le propre. Céline veut aider. Elle prend un panier. Le panier glisse. Les chaussettes tombent. Le sol est couvert. Céline a le ventre serré. Elle va vers papa. Papa, le panier est tombé. Papa s'approche. Merci de raconter. On ramasse ensemble. Céline prend une chaussette. Papa tient le panier. Maman entre. Maman, j'ai raconté. Le panier est tombé. Maman écoute. Merci Céline. On raconte à papa ou maman. C'est comme ça.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Céline est dans le salon. Papa plie le linge. Ça sent le propre. Céline veut aider. Elle prend un panier. Le panier glisse. Les chaussettes tombent. Le sol est couvert. Céline a le ventre serré. Elle va vers papa.
+enfant-f|Papa, le panier est tombé. Papa s'approche.
+papa|Merci de raconter. On ramasse ensemble.
+narrateur|Céline prend une chaussette. Papa tient le panier. Maman entre.
+enfant-f|Maman, j'ai raconté.
+narrateur|Le panier est tombé. Maman écoute.
+maman|Merci Céline. On raconte à papa ou maman. C'est comme ça.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le panier est tombé. Que fait Céline ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Céline a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Raconter aide.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le sol est propre. Céline se lave les mains. Papa plie encore une chaussette.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-08.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 maman|Merci Céline. On raconte à papa ou maman. C'est comme ça.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Le panier est tombé. Que fait Céline ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Céline a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Raconter aide.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Le sol est propre. Céline se lave les mains. Papa plie encore une chaussette.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.VER.001-08.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Céline raconte le panier</t>
+          <t>Chouchou raconte le panier</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une chaussette sèche sur le radiateur. Le panier glisse. Chouchou raconte. Papa et maman ramassent avec lui.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Céline est dans le salon. Papa plie le linge. Ça sent le propre. Céline veut aider. Elle prend un panier. Le panier glisse. Les chaussettes tombent. Le sol est couvert. Céline a le ventre serré. Elle va vers papa. Papa, le panier est tombé. Papa s'approche. Merci de raconter. On ramasse ensemble. Céline prend une chaussette. Papa tient le panier. Maman entre. Maman, j'ai raconté. Le panier est tombé. Maman écoute. Merci Céline. On raconte à papa ou maman. C'est comme ça.</t>
+          <t>Une chaussette sèche sur le radiateur. Elle est chaude et douce. Ça sent le savon propre. L'horloge fait tic, tic. Le tapis est beige et plat. Un rayon touche le panier. Papa plie le linge. Le linge est encore tiède. Maman range une serviette. Chouchou, tu sens le propre ? Oui, papa. Ça sent bon. C'est le savon doux. On plie ensemble. En ce moment, Chouchou veut aider. Un panier d'osier attend. L'osier est un peu rêche. Chouchou prend le panier. Le panier glisse. Les chaussettes tombent. Le sol est couvert. Une chaussette bleue. Une chaussette rouge. Une chaussette jaune aussi. Chouchou a le ventre serré. Il va vers papa. Papa, le panier est tombé. Merci de raconter. On ramasse ensemble. Papa tient le panier. Chouchou prend une chaussette. Elle est encore tiède. Elle est chaude. Oui. On la met dedans. Chouchou met la chaussette. Papa met l'autre. Maman s'approche. Je vous aide ? Maman, j'ai raconté. Le panier est tombé. Merci, Chouchou. On raconte à papa ou maman. C'est comme ça. Le sol redevient clair. Bravo, Chouchou. Tu as fait du bon travail. La bleue est dedans. La rouge aussi. La chaussette du radiateur reste là. Elle sèche encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Céline est dans le salon. Papa plie le linge. Ça sent le propre. Céline veut aider. Elle prend un panier. Le panier glisse. Les chaussettes tombent. Le sol est couvert. Céline a le ventre serré. Elle va vers papa.
-enfant-f|Papa, le panier est tombé. Papa s'approche.
-papa|Merci de raconter. On ramasse ensemble.
-narrateur|Céline prend une chaussette. Papa tient le panier. Maman entre.
-enfant-f|Maman, j'ai raconté.
-narrateur|Le panier est tombé. Maman écoute.
-maman|Merci Céline. On raconte à papa ou maman. C'est comme ça.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une chaussette sèche sur le radiateur.
+narrateur|Elle est chaude et douce.
+narrateur|Ça sent le savon propre.
+narrateur|L'horloge fait tic, tic.
+narrateur|Le tapis est beige et plat.
+narrateur|Un rayon touche le panier.
+narrateur|Papa plie le linge.
+narrateur|Le linge est encore tiède.
+narrateur|Maman range une serviette.
+papa|Chouchou, tu sens le propre ?
+enfant-m|Oui, papa.
+enfant-m|Ça sent bon.
+maman|C'est le savon doux.
+papa|On plie ensemble.
+narrateur|En ce moment, Chouchou veut aider.
+narrateur|Un panier d'osier attend.
+narrateur|L'osier est un peu rêche.
+narrateur|Chouchou prend le panier.
+narrateur|Le panier glisse.
+narrateur|Les chaussettes tombent.
+narrateur|Le sol est couvert.
+narrateur|Une chaussette bleue.
+narrateur|Une chaussette rouge.
+narrateur|Une chaussette jaune aussi.
+narrateur|Chouchou a le ventre serré.
+narrateur|Il va vers papa.
+enfant-m|Papa, le panier est tombé.
+papa|Merci de raconter.
+papa|On ramasse ensemble.
+narrateur|Papa tient le panier.
+narrateur|Chouchou prend une chaussette.
+narrateur|Elle est encore tiède.
+enfant-m|Elle est chaude.
+papa|Oui.
+papa|On la met dedans.
+narrateur|Chouchou met la chaussette.
+narrateur|Papa met l'autre.
+narrateur|Maman s'approche.
+maman|Je vous aide ?
+enfant-m|Maman, j'ai raconté.
+enfant-m|Le panier est tombé.
+maman|Merci, Chouchou.
+maman|On raconte à papa ou maman.
+maman|C'est comme ça.
+narrateur|Le sol redevient clair.
+papa|Bravo, Chouchou.
+papa|Tu as fait du bon travail.
+maman|La bleue est dedans.
+enfant-m|La rouge aussi.
+narrateur|La chaussette du radiateur reste là.
+narrateur|Elle sèche encore.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1401,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le panier est tombé. Que fait Céline ?</t>
+          <t>Le panier est tombé. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,10 +1557,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le panier est tombé. Que fait Céline ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Le panier est tombé.
+narrateur|Que fait Chouchou ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,7 +1585,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Céline a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Raconter aide.</t>
+          <t>Chouchou a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Tu as dit ça à papa ? Oui, papa. Bravo. Raconter aide. Le panier est plein. L'osier gratte un peu. Le tapis est propre. On plie encore une paire ? Oui. Papa plie la paire jaune.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,10 +1729,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Céline a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Raconter aide.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Chouchou a raconté.
+narrateur|Papa a écouté.
+narrateur|Maman a écouté.
+narrateur|Ensemble, ils ont ramassé.
+papa|Tu as dit ça à papa ?
+enfant-m|Oui, papa.
+maman|Bravo.
+maman|Raconter aide.
+narrateur|Le panier est plein.
+narrateur|L'osier gratte un peu.
+narrateur|Le tapis est propre.
+papa|On plie encore une paire ?
+enfant-m|Oui.
+narrateur|Papa plie la paire jaune.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1702,7 +1769,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le sol est propre. Céline se lave les mains. Papa plie encore une chaussette.</t>
+          <t>Le sol est propre. On se lave les mains ? Oui, papa. Chouchou se lave les mains. L'eau est tiède. Tu as fini tes mains ? Oui. Bravo. Je prends la serviette. Maman tend la serviette. Elle est douce. Papa plie encore une chaussette. Elle sent le savon.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,10 +1909,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le sol est propre. Céline se lave les mains. Papa plie encore une chaussette.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le sol est propre.
+papa|On se lave les mains ?
+enfant-m|Oui, papa.
+narrateur|Chouchou se lave les mains.
+narrateur|L'eau est tiède.
+papa|Tu as fini tes mains ?
+enfant-m|Oui.
+papa|Bravo.
+maman|Je prends la serviette.
+narrateur|Maman tend la serviette.
+narrateur|Elle est douce.
+narrateur|Papa plie encore une chaussette.
+narrateur|Elle sent le savon.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1870,7 +1948,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le panier est rangé. Merci d'avoir raconté. On raconte à papa ou maman. Oui. La chaussette sèche encore. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,10 +2088,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le panier est rangé.
+maman|Merci d'avoir raconté.
+papa|On raconte à papa ou maman.
+enfant-m|Oui.
+narrateur|La chaussette sèche encore.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2152,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-08.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-08.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une chaussette sèche sur le radiateur. Elle est chaude et douce. Ça sent le savon propre. L'horloge fait tic, tic. Le tapis est beige et plat. Un rayon touche le panier. Papa plie le linge. Le linge est encore tiède. Maman range une serviette. Chouchou, tu sens le propre ? Oui, papa. Ça sent bon. C'est le savon doux. On plie ensemble. En ce moment, Chouchou veut aider. Un panier d'osier attend. L'osier est un peu rêche. Chouchou prend le panier. Le panier glisse. Les chaussettes tombent. Le sol est couvert. Une chaussette bleue. Une chaussette rouge. Une chaussette jaune aussi. Chouchou a le ventre serré. Il va vers papa. Papa, le panier est tombé. Merci de raconter. On ramasse ensemble. Papa tient le panier. Chouchou prend une chaussette. Elle est encore tiède. Elle est chaude. Oui. On la met dedans. Chouchou met la chaussette. Papa met l'autre. Maman s'approche. Je vous aide ? Maman, j'ai raconté. Le panier est tombé. Merci, Chouchou. On raconte à papa ou maman. C'est comme ça. Le sol redevient clair. Bravo, Chouchou. Tu as fait du bon travail. La bleue est dedans. La rouge aussi. La chaussette du radiateur reste là. Elle sèche encore.</t>
+          <t>Une chaussette sèche sur le radiateur. Elle est chaude et douce. Ça sent le savon propre. L'horloge fait tic, tic. Le tapis est beige et plat. La fenêtre est un peu embuée. Un oiseau passe dehors. Un rayon touche le panier. Papa plie le linge. Le linge est encore tiède. Maman range une serviette. Chouchou, tu sens le propre ? Oui, papa. Ça sent bon. C'est le savon doux. On plie ensemble. En ce moment, Chouchou veut aider. Un panier d'osier attend. L'osier est un peu rêche. Chouchou prend le panier. Le panier glisse. Les chaussettes tombent. Le sol est couvert. Une chaussette bleue. Une chaussette rouge. Une chaussette jaune aussi. Chouchou a le ventre serré. Il va vers papa. Papa, le panier est tombé. Merci de raconter. On ramasse ensemble. Papa tient le panier. Chouchou prend une chaussette. Elle est encore tiède. Elle est chaude. Oui. On la met dedans. Chouchou met la chaussette. Papa met l'autre. Maman s'approche. Je vous aide ? Maman, j'ai raconté. Le panier est tombé. Merci, Chouchou. On raconte à papa ou maman. C'est comme ça. Le sol redevient clair. Bravo, Chouchou. La bleue est dedans. La rouge aussi. La chaussette du radiateur reste là. Elle sèche encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Céline est dans le salon. Papa plie le linge. Ça sent le propre. Céline veut aider. Elle prend un panier. Le panier glisse. Les chaussettes tombent. Le sol est couvert. Céline a le ventre serré. Elle va vers papa. Céline dit : papa, le panier est tombé. Papa s'approche. Papa dit : merci de &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt;. On ramasse ensemble. Céline prend une chaussette. Papa tient le panier. Maman entre. Céline dit : maman, j'ai raconté. Le panier est tombé. Maman écoute. Maman dit : merci Céline. On raconte à papa ou maman. C'est comme ça.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une chaussette sèche sur le radiateur. Elle est chaude et douce. Ça sent le savon propre. L'horloge fait tic, tic. Le tapis est beige et plat. La fenêtre est un peu embuée. Un oiseau passe dehors. Un rayon touche le panier. Papa plie le linge. Le linge est encore tiède. Maman range une serviette. Chouchou, tu sens le propre ? Oui, papa. Ça sent bon. C'est le savon doux. On plie ensemble. En ce moment, Chouchou veut aider. Un panier d'osier attend. L'osier est un peu rêche. Chouchou prend le panier. Le panier glisse. Les chaussettes tombent. Le sol est couvert. Une chaussette bleue. Une chaussette rouge. Une chaussette jaune aussi. Chouchou a le ventre serré. Il va vers papa. Papa, le panier est tombé. Merci de raconter. On ramasse ensemble. Papa tient le panier. Chouchou prend une chaussette. Elle est encore tiède. Elle est chaude. Oui. On la met dedans. Chouchou met la chaussette. Papa met l'autre. Maman s'approche. Je vous aide ? Maman, j'ai raconté. Le panier est tombé. Merci, Chouchou. On raconte à papa ou maman. C'est comme ça. Le sol redevient clair. Bravo, Chouchou. La bleue est dedans. La rouge aussi. La chaussette du radiateur reste là. Elle sèche encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1329,6 +1329,8 @@
 narrateur|Ça sent le savon propre.
 narrateur|L'horloge fait tic, tic.
 narrateur|Le tapis est beige et plat.
+narrateur|La fenêtre est un peu embuée.
+narrateur|Un oiseau passe dehors.
 narrateur|Un rayon touche le panier.
 narrateur|Papa plie le linge.
 narrateur|Le linge est encore tiède.
@@ -1370,7 +1372,6 @@
 maman|C'est comme ça.
 narrateur|Le sol redevient clair.
 papa|Bravo, Chouchou.
-papa|Tu as fait du bon travail.
 maman|La bleue est dedans.
 enfant-m|La rouge aussi.
 narrateur|La chaussette du radiateur reste là.
@@ -1406,7 +1407,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le panier est tombé. Que fait Céline ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le panier est tombé. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1585,12 +1586,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Tu as dit ça à papa ? Oui, papa. Bravo. Raconter aide. Le panier est plein. L'osier gratte un peu. Le tapis est propre. On plie encore une paire ? Oui. Papa plie la paire jaune.</t>
+          <t>Chouchou a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Tu as dit ça à papa ? Oui, papa. Bravo. Raconter aide. Le panier est plein. L'osier gratte un peu. Le tapis est propre. On plie encore une paire ? Oui. Papa plie la paire jaune. Elle est toute douce. Oui. Le savon sent encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Céline a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. &lt;emphasis level="moderate"&gt;raconter&lt;/emphasis&gt; aide.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a raconté. Papa a écouté. Maman a écouté. Ensemble, ils ont ramassé. Tu as dit ça à papa ? Oui, papa. Bravo. Raconter aide. Le panier est plein. L'osier gratte un peu. Le tapis est propre. On plie encore une paire ? Oui. Papa plie la paire jaune. Elle est toute douce. Oui. Le savon sent encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1742,7 +1743,10 @@
 narrateur|Le tapis est propre.
 papa|On plie encore une paire ?
 enfant-m|Oui.
-narrateur|Papa plie la paire jaune.</t>
+narrateur|Papa plie la paire jaune.
+maman|Elle est toute douce.
+enfant-m|Oui.
+narrateur|Le savon sent encore.</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1778,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le sol est propre. Céline se lave les mains. &lt;emphasis level="moderate"&gt;papa&lt;/emphasis&gt; plie encore une chaussette.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le sol est propre. On se lave les mains ? Oui, papa. Chouchou se lave les mains. L'eau est tiède. Tu as fini tes mains ? Oui. Bravo. Je prends la serviette. Maman tend la serviette. Elle est douce. Papa plie encore une chaussette. Elle sent le savon.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1948,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le panier est rangé. Merci d'avoir raconté. On raconte à papa ou maman. Oui. La chaussette sèche encore. L'histoire est finie.</t>
+          <t>Le panier est rangé. Merci d'avoir raconté. On raconte à papa ou maman. Oui. La chaussette sèche encore.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le panier est rangé. Merci d'avoir raconté. On raconte à papa ou maman. Oui. La chaussette sèche encore.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2092,8 +2096,7 @@
 maman|Merci d'avoir raconté.
 papa|On raconte à papa ou maman.
 enfant-m|Oui.
-narrateur|La chaussette sèche encore.
-narrateur|L'histoire est finie.</t>
+narrateur|La chaussette sèche encore.</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2159,6 +2162,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.VER.001-08.xlsx
+++ b/stories/arbres/ATOM-FAM.VER.001-08.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>salon, linge chaud, radiateur</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Céline, papa, maman</t>
+          <t>Chouchou, papa, maman</t>
         </is>
       </c>
     </row>
